--- a/artfynd/A 1706-2026 artfynd.xlsx
+++ b/artfynd/A 1706-2026 artfynd.xlsx
@@ -1118,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133157016</v>
+        <v>133170946</v>
       </c>
       <c r="B6" t="n">
-        <v>57958</v>
+        <v>58119</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,29 +1129,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1161,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>306865</v>
+        <v>306825</v>
       </c>
       <c r="R6" t="n">
-        <v>6521129</v>
+        <v>6521163</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,11 +1205,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Noterades i aktuell avverkningsanmälan av kontinuitesskog som är en del av den artskyddade tretåiga hackspettens revir.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133170946</v>
+        <v>133157016</v>
       </c>
       <c r="B7" t="n">
-        <v>58119</v>
+        <v>57958</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1239,37 +1242,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1279,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>306825</v>
+        <v>306865</v>
       </c>
       <c r="R7" t="n">
-        <v>6521163</v>
+        <v>6521129</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,6 +1310,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Noterades i aktuell avverkningsanmälan av kontinuitesskog som är en del av den artskyddade tretåiga hackspettens revir.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 1706-2026 artfynd.xlsx
+++ b/artfynd/A 1706-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133157038</v>
       </c>
       <c r="B2" t="n">
-        <v>79419</v>
+        <v>79420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1118,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133170946</v>
+        <v>133157016</v>
       </c>
       <c r="B6" t="n">
-        <v>58119</v>
+        <v>57958</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,37 +1129,29 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1169,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>306825</v>
+        <v>306865</v>
       </c>
       <c r="R6" t="n">
-        <v>6521163</v>
+        <v>6521129</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,6 +1197,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Noterades i aktuell avverkningsanmälan av kontinuitesskog som är en del av den artskyddade tretåiga hackspettens revir.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133157016</v>
+        <v>133170946</v>
       </c>
       <c r="B7" t="n">
-        <v>57958</v>
+        <v>58119</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1242,29 +1239,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1274,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>306865</v>
+        <v>306825</v>
       </c>
       <c r="R7" t="n">
-        <v>6521129</v>
+        <v>6521163</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,11 +1315,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Noterades i aktuell avverkningsanmälan av kontinuitesskog som är en del av den artskyddade tretåiga hackspettens revir.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 1706-2026 artfynd.xlsx
+++ b/artfynd/A 1706-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133157038</v>
       </c>
       <c r="B2" t="n">
-        <v>79420</v>
+        <v>79434</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>133156841</v>
       </c>
       <c r="B3" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>133156948</v>
       </c>
       <c r="B4" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>133157219</v>
       </c>
       <c r="B5" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133157016</v>
+        <v>133170946</v>
       </c>
       <c r="B6" t="n">
-        <v>57958</v>
+        <v>58126</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,29 +1129,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1161,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>306865</v>
+        <v>306825</v>
       </c>
       <c r="R6" t="n">
-        <v>6521129</v>
+        <v>6521163</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,11 +1205,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Noterades i aktuell avverkningsanmälan av kontinuitesskog som är en del av den artskyddade tretåiga hackspettens revir.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133170946</v>
+        <v>133157016</v>
       </c>
       <c r="B7" t="n">
-        <v>58119</v>
+        <v>57965</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1239,37 +1242,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1279,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>306825</v>
+        <v>306865</v>
       </c>
       <c r="R7" t="n">
-        <v>6521163</v>
+        <v>6521129</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,6 +1310,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Noterades i aktuell avverkningsanmälan av kontinuitesskog som är en del av den artskyddade tretåiga hackspettens revir.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 1706-2026 artfynd.xlsx
+++ b/artfynd/A 1706-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>133157038</v>
       </c>
       <c r="B2" t="n">
-        <v>79434</v>
+        <v>79459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -776,27 +776,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133156841</v>
+        <v>133157219</v>
       </c>
       <c r="B3" t="n">
-        <v>57965</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -804,12 +804,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -819,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>306767</v>
+        <v>306876</v>
       </c>
       <c r="R3" t="n">
-        <v>6521092</v>
+        <v>6521119</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,7 +871,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Noterades i avverkningsanmälan</t>
+          <t>Den avverkningsplanerade olikåldriga och flerskitade kontinuitetssskogen utgör en viktig del av spillkråkans revir</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133156948</v>
+        <v>133156841</v>
       </c>
       <c r="B4" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>306804</v>
+        <v>306767</v>
       </c>
       <c r="R4" t="n">
-        <v>6521123</v>
+        <v>6521092</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +981,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Noterades i aktuell avverkningsanmälan</t>
+          <t>Noterades i avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133157219</v>
+        <v>133156948</v>
       </c>
       <c r="B5" t="n">
-        <v>57962</v>
+        <v>57975</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,16 +1019,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1024,24 +1036,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>306876</v>
+        <v>306804</v>
       </c>
       <c r="R5" t="n">
-        <v>6521119</v>
+        <v>6521123</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Den avverkningsplanerade olikåldriga och flerskitade kontinuitetssskogen utgör en viktig del av spillkråkans revir</t>
+          <t>Noterades i aktuell avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133170946</v>
+        <v>133157016</v>
       </c>
       <c r="B6" t="n">
-        <v>58126</v>
+        <v>57975</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,37 +1129,29 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1169,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>306825</v>
+        <v>306865</v>
       </c>
       <c r="R6" t="n">
-        <v>6521163</v>
+        <v>6521129</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,6 +1197,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Noterades i aktuell avverkningsanmälan av kontinuitesskog som är en del av den artskyddade tretåiga hackspettens revir.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133157016</v>
+        <v>133170946</v>
       </c>
       <c r="B7" t="n">
-        <v>57965</v>
+        <v>58136</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1242,29 +1239,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1274,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>306865</v>
+        <v>306825</v>
       </c>
       <c r="R7" t="n">
-        <v>6521129</v>
+        <v>6521163</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,11 +1317,6 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Noterades i aktuell avverkningsanmälan av kontinuitesskog som är en del av den artskyddade tretåiga hackspettens revir.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1338,6 +1338,120 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133157118</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Flöttemarken, Boh</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>306828</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6521112</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Naverstad</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Stationär i den gamla kontinuitesskogen som är planerade för avverkning dvs. har hemvist</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1706-2026 artfynd.xlsx
+++ b/artfynd/A 1706-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133157038</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133157219</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133156841</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133156948</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1225,6 +1250,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133157016</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133170946</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1452,8 +1487,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133157118</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>